--- a/rules/CORE-000024/positive/01/data/unit-test-coreid-CG0082-positive.xlsx
+++ b/rules/CORE-000024/positive/01/data/unit-test-coreid-CG0082-positive.xlsx
@@ -1068,7 +1068,7 @@
           <t>Nervous system disorders</t>
         </is>
       </c>
-      <c r="I5" s="9" t="n">
+      <c r="I5" s="10" t="n">
         <v>3</v>
       </c>
       <c r="J5" s="7" t="inlineStr">
@@ -1150,7 +1150,7 @@
           <t>Musculoskeletal and connective tissue disorders</t>
         </is>
       </c>
-      <c r="I6" s="9" t="n">
+      <c r="I6" s="10" t="n">
         <v>6</v>
       </c>
       <c r="J6" s="7" t="inlineStr">
@@ -1227,7 +1227,7 @@
           <t>Vascular disorders</t>
         </is>
       </c>
-      <c r="I7" s="9" t="n">
+      <c r="I7" s="10" t="n">
         <v>7</v>
       </c>
       <c r="J7" s="7" t="inlineStr">
@@ -1319,7 +1319,7 @@
           <t>Nervous system disorders</t>
         </is>
       </c>
-      <c r="I8" s="9" t="n">
+      <c r="I8" s="10" t="n">
         <v>4</v>
       </c>
       <c r="J8" s="7" t="inlineStr">
@@ -1401,7 +1401,7 @@
           <t>Musculoskeletal and connective tissue disorders</t>
         </is>
       </c>
-      <c r="I9" s="9" t="n">
+      <c r="I9" s="10" t="n">
         <v>5</v>
       </c>
       <c r="J9" s="7" t="inlineStr">
@@ -1478,7 +1478,7 @@
           <t>Vascular disorders</t>
         </is>
       </c>
-      <c r="I10" s="9" t="n">
+      <c r="I10" s="10" t="n">
         <v>2</v>
       </c>
       <c r="J10" s="7" t="inlineStr">
